--- a/activity_sports_waivers_forms/042_sports_co_op_registration_and_waiver--activity_sports_waivers_forms.xlsx
+++ b/activity_sports_waivers_forms/042_sports_co_op_registration_and_waiver--activity_sports_waivers_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_have_read_and_agree_to_the_terms_and_conditions',_'value':_true}</t>
+          <t>i_have_read_and_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I have read and agree to the terms and conditions', 'value': True}</t>
+          <t>I have read and agree to the terms and conditions</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'i_have_not_read_and_do_not_agree_to_the_terms_and_conditions',_'value':_false}</t>
+          <t>i_have_not_read_and_do_not_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'I have not read and do not agree to the terms and conditions', 'value': False}</t>
+          <t>I have not read and do not agree to the terms and conditions</t>
         </is>
       </c>
     </row>
